--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:25:22+00:00</t>
+    <t>2025-07-07T15:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:26:46+00:00</t>
+    <t>2025-10-08T07:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4638,7 +4638,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:41:56+00:00</t>
+    <t>2025-10-08T15:42:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
